--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14514,7 +14514,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15476,7 +15476,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15538,7 +15538,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15856,7 +15856,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15980,7 +15980,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17112,7 +17112,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17368,7 +17368,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17554,7 +17554,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17810,7 +17810,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17872,7 +17872,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -18120,7 +18120,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18376,7 +18376,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18500,7 +18500,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18562,7 +18562,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18624,7 +18624,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18826,7 +18826,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18950,7 +18950,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -19136,7 +19136,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19462,7 +19462,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19586,7 +19586,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19648,7 +19648,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19850,7 +19850,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19974,7 +19974,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -20036,7 +20036,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -20098,7 +20098,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -20160,7 +20160,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -20362,7 +20362,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20610,7 +20610,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20672,7 +20672,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -21068,7 +21068,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -21130,7 +21130,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -21192,7 +21192,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -21324,7 +21324,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21386,7 +21386,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21510,7 +21510,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21952,7 +21952,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -22014,7 +22014,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -22076,7 +22076,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -22332,7 +22332,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22394,7 +22394,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22456,7 +22456,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22518,7 +22518,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22650,7 +22650,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22782,7 +22782,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22844,7 +22844,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22906,7 +22906,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -23100,7 +23100,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -23364,7 +23364,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23822,7 +23822,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -24738,7 +24738,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24800,7 +24800,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -25204,7 +25204,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -25266,7 +25266,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -25398,7 +25398,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25855,7 +25855,7 @@
         </is>
       </c>
       <c r="E399" s="4" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F399" s="3" t="inlineStr">
         <is>
@@ -25864,14 +25864,14 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
         <v>13192000</v>
       </c>
       <c r="I399" s="5" t="n">
-        <v>29982</v>
+        <v>30050</v>
       </c>
       <c r="J399" s="3" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>13192000</v>
       </c>
       <c r="L399" s="5" t="n">
-        <v>29982</v>
+        <v>30050</v>
       </c>
       <c r="M399" s="3" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -26128,7 +26128,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -26190,7 +26190,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -26322,7 +26322,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -26656,7 +26656,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -26788,7 +26788,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -27510,7 +27510,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -27968,7 +27968,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -28030,7 +28030,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -28418,7 +28418,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -28480,7 +28480,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -28806,7 +28806,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -28868,7 +28868,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -28930,7 +28930,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -29124,7 +29124,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -29256,7 +29256,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -29512,7 +29512,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -29574,7 +29574,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -29706,7 +29706,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -29962,7 +29962,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -30024,7 +30024,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -30156,7 +30156,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -30218,7 +30218,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -30412,7 +30412,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -30474,7 +30474,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -30606,7 +30606,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -30862,7 +30862,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -30924,7 +30924,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -31056,7 +31056,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -31118,7 +31118,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H481" s="5" t="n">
@@ -31312,7 +31312,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="H483" s="5" t="n">
@@ -31506,7 +31506,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -31568,7 +31568,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H487" s="5" t="n">
@@ -31630,7 +31630,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -31956,7 +31956,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -32018,7 +32018,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H494" s="5" t="n">
@@ -32080,7 +32080,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -32406,7 +32406,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H500" s="5" t="n">
@@ -32468,7 +32468,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -32530,7 +32530,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H502" s="5" t="n">
@@ -32724,7 +32724,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
@@ -32856,7 +32856,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H507" s="5" t="n">
@@ -32918,7 +32918,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H508" s="5" t="n">
@@ -32980,7 +32980,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -33112,7 +33112,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H514" s="5" t="n">
@@ -33368,7 +33368,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H515" s="5" t="n">
@@ -33756,7 +33756,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H521" s="5" t="n">
@@ -33818,7 +33818,7 @@
       </c>
       <c r="G522" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H522" s="5" t="n">
@@ -34206,7 +34206,7 @@
       </c>
       <c r="G528" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H528" s="5" t="n">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="G529" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H529" s="5" t="n">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="G533" s="3" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="H533" s="5" t="n">
@@ -34586,7 +34586,7 @@
       </c>
       <c r="G534" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H534" s="5" t="n">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="G535" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H535" s="5" t="n">
@@ -34710,7 +34710,7 @@
       </c>
       <c r="G536" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H536" s="5" t="n">
@@ -34772,7 +34772,7 @@
       </c>
       <c r="G537" s="3" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H537" s="5" t="n">
@@ -36232,7 +36232,7 @@
       </c>
       <c r="G559" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H559" s="5" t="n">
@@ -36698,7 +36698,7 @@
       </c>
       <c r="G566" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H566" s="5" t="n">
@@ -36760,7 +36760,7 @@
       </c>
       <c r="G567" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H567" s="5" t="n">
@@ -37156,7 +37156,7 @@
       </c>
       <c r="G573" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H573" s="5" t="n">
@@ -37622,7 +37622,7 @@
       </c>
       <c r="G580" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H580" s="5" t="n">
@@ -37684,7 +37684,7 @@
       </c>
       <c r="G581" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H581" s="5" t="n">
@@ -38950,7 +38950,7 @@
       </c>
       <c r="G600" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H600" s="5" t="n">
@@ -39012,7 +39012,7 @@
       </c>
       <c r="G601" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H601" s="5" t="n">
@@ -39882,7 +39882,7 @@
       </c>
       <c r="G614" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H614" s="5" t="n">
@@ -39944,7 +39944,7 @@
       </c>
       <c r="G615" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H615" s="5" t="n">
@@ -40348,7 +40348,7 @@
       </c>
       <c r="G621" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H621" s="5" t="n">
@@ -40410,7 +40410,7 @@
       </c>
       <c r="G622" s="3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H622" s="5" t="n">
@@ -40472,7 +40472,7 @@
       </c>
       <c r="G623" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H623" s="5" t="n">
@@ -40868,7 +40868,7 @@
       </c>
       <c r="G629" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H629" s="5" t="n">
@@ -41000,7 +41000,7 @@
       </c>
       <c r="G631" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H631" s="5" t="n">
@@ -41326,7 +41326,7 @@
       </c>
       <c r="G636" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H636" s="5" t="n">
@@ -41730,7 +41730,7 @@
       </c>
       <c r="G642" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H642" s="5" t="n">
@@ -41792,7 +41792,7 @@
       </c>
       <c r="G643" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H643" s="5" t="n">
@@ -42196,7 +42196,7 @@
       </c>
       <c r="G649" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H649" s="5" t="n">
@@ -42258,7 +42258,7 @@
       </c>
       <c r="G650" s="3" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="H650" s="5" t="n">
@@ -44130,7 +44130,7 @@
       </c>
       <c r="G678" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H678" s="5" t="n">
@@ -44262,7 +44262,7 @@
       </c>
       <c r="G680" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H680" s="5" t="n">
@@ -44720,7 +44720,7 @@
       </c>
       <c r="G687" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H687" s="5" t="n">
@@ -46037,7 +46037,7 @@
           <t>A | 493呎 (2房)
 $1040万
 $21,089/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -46045,7 +46045,7 @@
           <t>B | 305呎 (1房)
 $589万
 $19,311/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -46053,7 +46053,7 @@
           <t>C | 305呎 (1房)
 $596万
 $19,525/呎
-(25年-07月-31日)</t>
+(25年-08月-01日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -46061,7 +46061,7 @@
           <t>D | 305呎 (1房)
 $638万
 $20,925/呎
-(26年-03月-11日)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -46069,7 +46069,7 @@
           <t>E | 301呎 (1房)
 $638万
 $21,196/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -46085,7 +46085,7 @@
           <t>G | 437呎 (2房)
 $883万
 $20,208/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
     </row>
@@ -46100,7 +46100,7 @@
           <t>A | 493呎 (2房)
 $1018万
 $20,643/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -46108,7 +46108,7 @@
           <t>B | 305呎 (1房)
 $583万
 $19,121/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -46116,7 +46116,7 @@
           <t>C | 305呎 (1房)
 $590万
 $19,328/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -46124,7 +46124,7 @@
           <t>D | 305呎 (1房)
 $596万
 $19,541/呎
-(25年-06月-08日)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -46132,7 +46132,7 @@
           <t>E | 301呎 (1房)
 $625万
 $20,754/呎
-(25年-07月-29日)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -46148,7 +46148,7 @@
           <t>G | 437呎 (2房)
 $874万
 $20,007/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -46163,7 +46163,7 @@
           <t>A | 493呎 (2房)
 $1008万
 $20,440/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -46171,7 +46171,7 @@
           <t>B | 305呎 (1房)
 $577万
 $18,931/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -46179,7 +46179,7 @@
           <t>C | 305呎 (1房)
 $584万
 $19,138/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -46187,7 +46187,7 @@
           <t>D | 305呎 (1房)
 $590万
 $19,348/呎
-(25年-06月-10日)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -46195,7 +46195,7 @@
           <t>E | 301呎 (1房)
 $619万
 $20,551/呎
-(25年-07月-20日)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -46211,7 +46211,7 @@
           <t>G | 437呎 (2房)
 $866万
 $19,810/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -46226,7 +46226,7 @@
           <t>A | 493呎 (2房)
 $998万
 $20,237/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -46234,7 +46234,7 @@
           <t>B | 305呎 (1房)
 $578万
 $18,954/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -46242,7 +46242,7 @@
           <t>C | 305呎 (1房)
 $578万
 $18,951/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -46250,7 +46250,7 @@
           <t>D | 305呎 (1房)
 $584万
 $19,154/呎
-(25年-05月-25日)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -46258,7 +46258,7 @@
           <t>E | 301呎 (1房)
 $610万
 $20,249/呎
-(25年-07月-20日)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -46274,7 +46274,7 @@
           <t>G | 437呎 (2房)
 $867万
 $19,844/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -46289,7 +46289,7 @@
           <t>A | 493呎 (2房)
 $988万
 $20,034/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -46297,7 +46297,7 @@
           <t>B | 305呎 (1房)
 $572万
 $18,764/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -46305,7 +46305,7 @@
           <t>C | 305呎 (1房)
 $572万
 $18,761/呎
-(25年-05月-29日)</t>
+(25年-05月-30日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -46313,7 +46313,7 @@
           <t>D | 305呎 (1房)
 $578万
 $18,967/呎
-(25年-05月-25日)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -46321,7 +46321,7 @@
           <t>E | 301呎 (1房)
 $604万
 $20,050/呎
-(25年-07月-20日)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -46337,7 +46337,7 @@
           <t>G | 437呎 (2房)
 $849万
 $19,421/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
     </row>
@@ -46352,7 +46352,7 @@
           <t>A | 493呎 (2房)
 $983万
 $19,935/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -46360,7 +46360,7 @@
           <t>B | 305呎 (1房)
 $569万
 $18,669/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -46368,7 +46368,7 @@
           <t>C | 305呎 (1房)
 $569万
 $18,669/呎
-(25年-05月-18日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -46376,7 +46376,7 @@
           <t>D | 305呎 (1房)
 $576万
 $18,872/呎
-(25年-05月-25日)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -46384,7 +46384,7 @@
           <t>E | 301呎 (1房)
 $607万
 $20,169/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -46392,7 +46392,7 @@
           <t>F | 447呎 (2房)
 $909万
 $20,338/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -46400,7 +46400,7 @@
           <t>G | 437呎 (2房)
 $844万
 $19,323/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
     </row>
@@ -46415,7 +46415,7 @@
           <t>A | 493呎 (2房)
 $978万
 $19,838/呎
-(25年-05月-21日)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -46423,7 +46423,7 @@
           <t>B | 305呎 (1房)
 $567万
 $18,577/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -46431,7 +46431,7 @@
           <t>C | 305呎 (1房)
 $567万
 $18,577/呎
-(25年-04月-09日)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -46439,7 +46439,7 @@
           <t>D | 305呎 (1房)
 $573万
 $18,777/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -46447,7 +46447,7 @@
           <t>E | 301呎 (1房)
 $598万
 $19,854/呎
-(25年-07月-22日)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -46455,7 +46455,7 @@
           <t>F | 447呎 (2房)
 $905万
 $20,237/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -46463,7 +46463,7 @@
           <t>G | 437呎 (2房)
 $860万
 $19,682/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
     </row>
@@ -46541,7 +46541,7 @@
           <t>A | 493呎 (2房)
 $968万
 $19,641/呎
-(25年-05月-21日)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -46549,7 +46549,7 @@
           <t>B | 305呎 (1房)
 $561万
 $18,393/呎
-(25年-06月-02日)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -46557,7 +46557,7 @@
           <t>C | 305呎 (1房)
 $561万
 $18,390/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -46565,7 +46565,7 @@
           <t>D | 305呎 (1房)
 $567万
 $18,590/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -46573,7 +46573,7 @@
           <t>E | 301呎 (1房)
 $592万
 $19,654/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -46581,7 +46581,7 @@
           <t>F | 447呎 (2房)
 $896万
 $20,036/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -46589,7 +46589,7 @@
           <t>G | 437呎 (2房)
 $852万
 $19,485/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
     </row>
@@ -46604,7 +46604,7 @@
           <t>A | 493呎 (2房)
 $963万
 $19,542/呎
-(25年-05月-20日)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -46612,7 +46612,7 @@
           <t>B | 305呎 (1房)
 $558万
 $18,302/呎
-(25年-05月-29日)</t>
+(25年-05月-30日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -46620,7 +46620,7 @@
           <t>C | 305呎 (1房)
 $558万
 $18,298/呎
-(25年-04月-10日)</t>
+(25年-04月-11日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -46628,7 +46628,7 @@
           <t>D | 305呎 (1房)
 $564万
 $18,502/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -46636,7 +46636,7 @@
           <t>E | 301呎 (1房)
 $614万
 $20,402/呎
-(26年-03月-11日)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -46644,7 +46644,7 @@
           <t>F | 447呎 (2房)
 $891万
 $19,935/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -46652,7 +46652,7 @@
           <t>G | 437呎 (2房)
 $828万
 $18,941/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
     </row>
@@ -46667,7 +46667,7 @@
           <t>A | 493呎 (2房)
 $959万
 $19,444/呎
-(25年-05月-20日)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -46675,7 +46675,7 @@
           <t>B | 305呎 (1房)
 $568万
 $18,610/呎
-(25年-06月-03日)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -46683,7 +46683,7 @@
           <t>C | 305呎 (1房)
 $555万
 $18,207/呎
-(25年-06月-05日)</t>
+(25年-06月-06日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -46691,7 +46691,7 @@
           <t>D | 305呎 (1房)
 $561万
 $18,407/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -46699,7 +46699,7 @@
           <t>E | 301呎 (1房)
 $586万
 $19,458/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -46707,7 +46707,7 @@
           <t>F | 447呎 (2房)
 $887万
 $19,837/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -46715,7 +46715,7 @@
           <t>G | 437呎 (2房)
 $824万
 $18,849/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -46730,7 +46730,7 @@
           <t>A | 493呎 (2房)
 $954万
 $19,349/呎
-(25年-04月-09日)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -46738,7 +46738,7 @@
           <t>B | 305呎 (1房)
 $556万
 $18,216/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -46746,7 +46746,7 @@
           <t>C | 305呎 (1房)
 $553万
 $18,118/呎
-(25年-05月-29日)</t>
+(25年-05月-30日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -46754,7 +46754,7 @@
           <t>D | 305呎 (1房)
 $559万
 $18,315/呎
-(25年-05月-25日)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -46762,7 +46762,7 @@
           <t>E | 301呎 (1房)
 $583万
 $19,362/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -46770,7 +46770,7 @@
           <t>F | 447呎 (2房)
 $882万
 $19,738/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -46778,7 +46778,7 @@
           <t>G | 437呎 (2房)
 $820万
 $18,753/呎
-(25年-07月-31日)</t>
+(25年-08月-01日)</t>
         </is>
       </c>
     </row>
@@ -46793,7 +46793,7 @@
           <t>A | 493呎 (2房)
 $949万
 $19,252/呎
-(25年-02月-18日)</t>
+(25年-02月-19日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -46801,7 +46801,7 @@
           <t>B | 305呎 (1房)
 $553万
 $18,128/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -46809,7 +46809,7 @@
           <t>C | 305呎 (1房)
 $550万
 $18,030/呎
-(25年-04月-13日)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -46817,7 +46817,7 @@
           <t>D | 305呎 (1房)
 $556万
 $18,223/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -46825,7 +46825,7 @@
           <t>E | 301呎 (1房)
 $577万
 $19,173/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -46833,7 +46833,7 @@
           <t>F | 447呎 (2房)
 $878万
 $19,640/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -46841,7 +46841,7 @@
           <t>G | 437呎 (2房)
 $815万
 $18,659/呎
-(25年-07月-20日)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
     </row>
@@ -46856,7 +46856,7 @@
           <t>A | 493呎 (2房)
 $933万
 $18,933/呎
-(25年-01月-06日)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -46864,7 +46864,7 @@
           <t>B | 305呎 (1房)
 $550万
 $18,036/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -46872,7 +46872,7 @@
           <t>C | 305呎 (1房)
 $547万
 $17,938/呎
-(25年-04月-13日)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -46880,7 +46880,7 @@
           <t>D | 305呎 (1房)
 $553万
 $18,131/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -46888,7 +46888,7 @@
           <t>E | 301呎 (1房)
 $574万
 $19,073/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -46896,7 +46896,7 @@
           <t>F | 447呎 (2房)
 $863万
 $19,315/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -46904,7 +46904,7 @@
           <t>G | 437呎 (2房)
 $802万
 $18,348/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -46919,7 +46919,7 @@
           <t>A | 493呎 (2房)
 $929万
 $18,838/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -46927,7 +46927,7 @@
           <t>B | 305呎 (1房)
 $538万
 $17,652/呎
-(24年-12月-16日)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -46935,7 +46935,7 @@
           <t>C | 305呎 (1房)
 $544万
 $17,846/呎
-(25年-01月-14日)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -46943,7 +46943,7 @@
           <t>D | 305呎 (1房)
 $550万
 $18,043/呎
-(25年-05月-20日)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -46951,7 +46951,7 @@
           <t>E | 301呎 (1房)
 $571万
 $18,980/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -46959,7 +46959,7 @@
           <t>F | 447呎 (2房)
 $859万
 $19,219/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -46967,7 +46967,7 @@
           <t>G | 437呎 (2房)
 $798万
 $18,256/呎
-(25年-05月-20日)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -46982,7 +46982,7 @@
           <t>A | 493呎 (2房)
 $924万
 $18,744/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -46990,7 +46990,7 @@
           <t>B | 305呎 (1房)
 $536万
 $17,564/呎
-(24年-12月-16日)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -46998,7 +46998,7 @@
           <t>C | 305呎 (1房)
 $542万
 $17,757/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -47006,7 +47006,7 @@
           <t>D | 305呎 (1房)
 $548万
 $17,951/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -47014,7 +47014,7 @@
           <t>E | 301呎 (1房)
 $568万
 $18,884/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -47022,7 +47022,7 @@
           <t>F | 447呎 (2房)
 $855万
 $19,123/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -47030,7 +47030,7 @@
           <t>G | 437呎 (2房)
 $794万
 $18,162/呎
-(25年-05月-06日)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -47045,7 +47045,7 @@
           <t>A | 493呎 (2房)
 $920万
 $18,651/呎
-(25年-03月-06日)</t>
+(25年-03月-07日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -47053,7 +47053,7 @@
           <t>B | 305呎 (1房)
 $533万
 $17,475/呎
-(24年-12月-30日)</t>
+(24年-12月-31日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -47061,7 +47061,7 @@
           <t>C | 305呎 (1房)
 $539万
 $17,669/呎
-(25年-04月-01日)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -47069,7 +47069,7 @@
           <t>D | 305呎 (1房)
 $557万
 $18,259/呎
-(25年-06月-01日)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -47077,7 +47077,7 @@
           <t>E | 301呎 (1房)
 $560万
 $18,608/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -47085,7 +47085,7 @@
           <t>F | 447呎 (2房)
 $851万
 $19,029/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
@@ -47108,7 +47108,7 @@
           <t>A | 493呎 (2房)
 $909万
 $18,442/呎
-(25年-02月-26日)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -47116,7 +47116,7 @@
           <t>B | 305呎 (1房)
 $529万
 $17,351/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -47124,7 +47124,7 @@
           <t>C | 305呎 (1房)
 $535万
 $17,544/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -47132,7 +47132,7 @@
           <t>D | 305呎 (1房)
 $541万
 $17,734/呎
-(25年-05月-06日)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -47140,7 +47140,7 @@
           <t>E | 301呎 (1房)
 $556万
 $18,475/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -47148,7 +47148,7 @@
           <t>F | 447呎 (2房)
 $850万
 $19,007/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -47156,7 +47156,7 @@
           <t>G | 437呎 (2房)
 $789万
 $18,055/呎
-(25年-06月-10日)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -47171,7 +47171,7 @@
           <t>A | 493呎 (2房)
 $905万
 $18,357/呎
-(25年-01月-13日)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -47179,7 +47179,7 @@
           <t>B | 305呎 (1房)
 $526万
 $17,233/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -47187,7 +47187,7 @@
           <t>C | 305呎 (1房)
 $531万
 $17,423/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -47195,7 +47195,7 @@
           <t>D | 305呎 (1房)
 $537万
 $17,613/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -47203,7 +47203,7 @@
           <t>E | 301呎 (1房)
 $552万
 $18,346/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -47211,7 +47211,7 @@
           <t>F | 447呎 (2房)
 $849万
 $18,998/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -47219,7 +47219,7 @@
           <t>G | 437呎 (2房)
 $786万
 $17,995/呎
-(25年-05月-18日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -47234,7 +47234,7 @@
           <t>A | 493呎 (2房)
 $898万
 $18,207/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -47242,7 +47242,7 @@
           <t>B | 305呎 (1房)
 $522万
 $17,111/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -47250,7 +47250,7 @@
           <t>C | 305呎 (1房)
 $528万
 $17,302/呎
-(25年-05月-26日)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -47258,7 +47258,7 @@
           <t>D | 305呎 (1房)
 $533万
 $17,489/呎
-(25年-05月-25日)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -47266,7 +47266,7 @@
           <t>E | 301呎 (1房)
 $548万
 $18,219/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -47274,7 +47274,7 @@
           <t>F | 447呎 (2房)
 $840万
 $18,792/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -47282,7 +47282,7 @@
           <t>G | 437呎 (2房)
 $780万
 $17,854/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -47297,7 +47297,7 @@
           <t>A | 493呎 (2房)
 $885万
 $17,955/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -47305,7 +47305,7 @@
           <t>B | 305呎 (1房)
 $518万
 $16,990/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -47313,7 +47313,7 @@
           <t>C | 305呎 (1房)
 $524万
 $17,180/呎
-(25年-04月-01日)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -47321,7 +47321,7 @@
           <t>D | 305呎 (1房)
 $530万
 $17,367/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -47329,7 +47329,7 @@
           <t>E | 301呎 (1房)
 $540万
 $17,930/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -47337,7 +47337,7 @@
           <t>F | 447呎 (2房)
 $826万
 $18,479/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -47345,7 +47345,7 @@
           <t>G | 437呎 (2房)
 $767万
 $17,556/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -47360,7 +47360,7 @@
           <t>A | 493呎 (2房)
 $876万
 $17,779/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -47368,7 +47368,7 @@
           <t>B | 305呎 (1房)
 $515万
 $16,872/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -47376,7 +47376,7 @@
           <t>C | 305呎 (1房)
 $520万
 $17,056/呎
-(25年-06月-03日)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -47384,7 +47384,7 @@
           <t>D | 305呎 (1房)
 $529万
 $17,341/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -47392,7 +47392,7 @@
           <t>E | 301呎 (1房)
 $530万
 $17,611/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
@@ -47408,7 +47408,7 @@
           <t>G | 437呎 (2房)
 $757万
 $17,327/呎
-(25年-07月-30日)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
     </row>
@@ -47423,7 +47423,7 @@
           <t>A | 493呎 (2房)
 $854万
 $17,312/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -47431,7 +47431,7 @@
           <t>B | 305呎 (1房)
 $514万
 $16,846/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -47439,7 +47439,7 @@
           <t>C | 305呎 (1房)
 $520万
 $17,033/呎
-(25年-06月-18日)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -47447,7 +47447,7 @@
           <t>D | 305呎 (1房)
 $531万
 $17,410/呎
-(25年-06月-01日)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -47455,7 +47455,7 @@
           <t>E | 301呎 (1房)
 $526万
 $17,488/呎
-(25年-06月-08日)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
@@ -47471,7 +47471,7 @@
           <t>G | 437呎 (2房)
 $746万
 $17,071/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -47486,7 +47486,7 @@
           <t>A | 493呎 (2房)
 $838万
 $17,008/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -47494,7 +47494,7 @@
           <t>B | 305呎 (1房)
 $513万
 $16,820/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -47502,7 +47502,7 @@
           <t>C | 305呎 (1房)
 $519万
 $17,007/呎
-(25年-08月-05日)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -47510,7 +47510,7 @@
           <t>D | 305呎 (1房)
 $524万
 $17,193/呎
-(25年-07月-28日)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -47518,7 +47518,7 @@
           <t>E | 301呎 (1房)
 $523万
 $17,369/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
@@ -47534,7 +47534,7 @@
           <t>G | 437呎 (2房)
 $733万
 $16,767/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -47696,7 +47696,7 @@
           <t>A | 440呎 (2房)
 $1072万
 $24,361/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -47720,7 +47720,7 @@
           <t>D | 245呎 (开放式)
 $554万
 $22,604/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -47728,7 +47728,7 @@
           <t>E | 246呎 (开放式)
 $474万
 $19,252/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -47736,7 +47736,7 @@
           <t>F | 246呎 (开放式)
 $476万
 $19,362/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -47744,7 +47744,7 @@
           <t>G | 300呎 (1房)
 $583万
 $19,427/呎
-(25年-07月-28日)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="I5" s="24" t="inlineStr">
@@ -47767,7 +47767,7 @@
           <t>A | 440呎 (2房)
 $907万
 $20,620/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -47791,7 +47791,7 @@
           <t>D | 245呎 (开放式)
 $487万
 $19,890/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -47799,7 +47799,7 @@
           <t>E | 246呎 (开放式)
 $469万
 $19,061/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -47807,7 +47807,7 @@
           <t>F | 246呎 (开放式)
 $472万
 $19,167/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -47815,7 +47815,7 @@
           <t>G | 300呎 (1房)
 $577万
 $19,230/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="I6" s="24" t="inlineStr">
@@ -47838,7 +47838,7 @@
           <t>A | 440呎 (2房)
 $909万
 $20,655/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -47862,7 +47862,7 @@
           <t>D | 245呎 (开放式)
 $482万
 $19,694/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -47870,7 +47870,7 @@
           <t>E | 246呎 (开放式)
 $464万
 $18,866/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -47878,7 +47878,7 @@
           <t>F | 246呎 (开放式)
 $467万
 $18,980/呎
-(25年-09月-06日)</t>
+(25年-09月-07日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -47886,7 +47886,7 @@
           <t>G | 300呎 (1房)
 $571万
 $19,043/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -47909,7 +47909,7 @@
           <t>A | 440呎 (2房)
 $889万
 $20,214/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -47933,7 +47933,7 @@
           <t>D | 245呎 (开放式)
 $478万
 $19,498/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -47941,7 +47941,7 @@
           <t>E | 246呎 (开放式)
 $454万
 $18,476/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -47949,7 +47949,7 @@
           <t>F | 246呎 (开放式)
 $462万
 $18,793/呎
-(25年-09月-07日)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -47957,7 +47957,7 @@
           <t>G | 300呎 (1房)
 $566万
 $18,853/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -47980,7 +47980,7 @@
           <t>A | 440呎 (2房)
 $881万
 $20,014/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -48004,7 +48004,7 @@
           <t>D | 245呎 (开放式)
 $468万
 $19,098/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -48012,7 +48012,7 @@
           <t>E | 246呎 (开放式)
 $450万
 $18,293/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -48020,7 +48020,7 @@
           <t>F | 246呎 (开放式)
 $458万
 $18,602/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -48028,7 +48028,7 @@
           <t>G | 300呎 (1房)
 $560万
 $18,667/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -48051,7 +48051,7 @@
           <t>A | 440呎 (2房)
 $886万
 $20,148/呎
-(25年-07月-29日)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -48075,7 +48075,7 @@
           <t>D | 245呎 (开放式)
 $460万
 $18,792/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -48083,7 +48083,7 @@
           <t>E | 246呎 (开放式)
 $448万
 $18,207/呎
-(25年-07月-29日)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -48091,7 +48091,7 @@
           <t>F | 246呎 (开放式)
 $450万
 $18,305/呎
-(25年-08月-25日)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -48099,7 +48099,7 @@
           <t>G | 300呎 (1房)
 $557万
 $18,570/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -48107,7 +48107,7 @@
           <t>H | 493呎 (2房)
 $1059万
 $21,473/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -48122,7 +48122,7 @@
           <t>A | 440呎 (2房)
 $882万
 $20,048/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -48146,7 +48146,7 @@
           <t>D | 245呎 (开放式)
 $458万
 $18,698/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -48154,7 +48154,7 @@
           <t>E | 247呎 (开放式)
 $446万
 $18,036/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -48162,7 +48162,7 @@
           <t>F | 246呎 (开放式)
 $448万
 $18,220/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -48170,7 +48170,7 @@
           <t>G | 300呎 (1房)
 $554万
 $18,480/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -48178,7 +48178,7 @@
           <t>H | 493呎 (2房)
 $1030万
 $20,895/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
     </row>
@@ -48264,7 +48264,7 @@
           <t>A | 440呎 (2房)
 $863万
 $19,616/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -48288,7 +48288,7 @@
           <t>D | 245呎 (开放式)
 $466万
 $19,029/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -48296,7 +48296,7 @@
           <t>E | 247呎 (开放式)
 $441万
 $17,862/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -48304,7 +48304,7 @@
           <t>F | 246呎 (开放式)
 $444万
 $18,037/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -48312,7 +48312,7 @@
           <t>G | 300呎 (1房)
 $549万
 $18,300/呎
-(25年-01月-20日)</t>
+(25年-01月-21日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -48320,7 +48320,7 @@
           <t>H | 493呎 (2房)
 $1020万
 $20,688/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
           <t>A | 440呎 (2房)
 $859万
 $19,520/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -48359,7 +48359,7 @@
           <t>D | 245呎 (开放式)
 $464万
 $18,931/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -48367,7 +48367,7 @@
           <t>E | 246呎 (开放式)
 $439万
 $17,846/呎
-(25年-07月-15日)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -48375,7 +48375,7 @@
           <t>F | 246呎 (开放式)
 $442万
 $17,947/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -48383,7 +48383,7 @@
           <t>G | 300呎 (1房)
 $546万
 $18,207/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -48391,7 +48391,7 @@
           <t>H | 493呎 (2房)
 $1015万
 $20,584/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -48406,7 +48406,7 @@
           <t>A | 440呎 (2房)
 $855万
 $19,423/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -48430,7 +48430,7 @@
           <t>D | 245呎 (开放式)
 $462万
 $18,841/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -48438,7 +48438,7 @@
           <t>E | 247呎 (开放式)
 $437万
 $17,684/呎
-(25年-07月-16日)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -48446,7 +48446,7 @@
           <t>F | 246呎 (开放式)
 $444万
 $18,053/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -48454,7 +48454,7 @@
           <t>G | 300呎 (1房)
 $544万
 $18,117/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -48462,7 +48462,7 @@
           <t>H | 493呎 (2房)
 $1010万
 $20,483/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
     </row>
@@ -48477,7 +48477,7 @@
           <t>A | 440呎 (2房)
 $850万
 $19,327/呎
-(25年-07月-31日)</t>
+(25年-08月-01日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -48501,7 +48501,7 @@
           <t>D | 245呎 (开放式)
 $447万
 $18,237/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -48509,7 +48509,7 @@
           <t>E | 246呎 (开放式)
 $435万
 $17,671/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -48517,7 +48517,7 @@
           <t>F | 246呎 (开放式)
 $437万
 $17,768/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -48525,7 +48525,7 @@
           <t>G | 300呎 (1房)
 $541万
 $18,027/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -48533,7 +48533,7 @@
           <t>H | 493呎 (2房)
 $1005万
 $20,379/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -48548,7 +48548,7 @@
           <t>A | 440呎 (2房)
 $846万
 $19,230/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -48572,7 +48572,7 @@
           <t>D | 245呎 (开放式)
 $445万
 $18,147/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -48580,7 +48580,7 @@
           <t>E | 247呎 (开放式)
 $432万
 $17,510/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -48588,7 +48588,7 @@
           <t>F | 246呎 (开放式)
 $435万
 $17,679/呎
-(25年-09月-02日)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -48596,7 +48596,7 @@
           <t>G | 300呎 (1房)
 $538万
 $17,937/呎
-(25年-01月-12日)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -48604,7 +48604,7 @@
           <t>H | 493呎 (2房)
 $1000万
 $20,278/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -48619,7 +48619,7 @@
           <t>A | 440呎 (2房)
 $822万
 $18,684/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -48643,7 +48643,7 @@
           <t>D | 245呎 (开放式)
 $457万
 $18,657/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -48651,7 +48651,7 @@
           <t>E | 247呎 (开放式)
 $430万
 $17,417/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -48659,7 +48659,7 @@
           <t>F | 246呎 (开放式)
 $433万
 $17,593/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -48667,7 +48667,7 @@
           <t>G | 300呎 (1房)
 $535万
 $17,847/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -48675,7 +48675,7 @@
           <t>H | 493呎 (2房)
 $1006万
 $20,404/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -48690,7 +48690,7 @@
           <t>A | 440呎 (2房)
 $818万
 $18,589/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -48714,7 +48714,7 @@
           <t>D | 245呎 (开放式)
 $455万
 $18,563/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -48722,7 +48722,7 @@
           <t>E | 246呎 (开放式)
 $428万
 $17,402/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -48730,7 +48730,7 @@
           <t>F | 246呎 (开放式)
 $431万
 $17,504/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -48738,7 +48738,7 @@
           <t>G | 300呎 (1房)
 $533万
 $17,757/呎
-(24年-12月-16日)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -48746,7 +48746,7 @@
           <t>H | 493呎 (2房)
 $990万
 $20,075/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -48761,7 +48761,7 @@
           <t>A | 440呎 (2房)
 $814万
 $18,498/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -48785,7 +48785,7 @@
           <t>D | 245呎 (开放式)
 $453万
 $18,473/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -48793,7 +48793,7 @@
           <t>E | 246呎 (开放式)
 $426万
 $17,317/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -48801,7 +48801,7 @@
           <t>F | 246呎 (开放式)
 $428万
 $17,415/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -48809,7 +48809,7 @@
           <t>G | 300呎 (1房)
 $530万
 $17,667/呎
-(25年-01月-06日)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -48817,7 +48817,7 @@
           <t>H | 493呎 (2房)
 $985万
 $19,976/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -48832,7 +48832,7 @@
           <t>A | 440呎 (2房)
 $810万
 $18,405/呎
-(25年-04月-06日)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -48856,7 +48856,7 @@
           <t>D | 245呎 (开放式)
 $450万
 $18,380/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -48864,7 +48864,7 @@
           <t>E | 247呎 (开放式)
 $424万
 $17,162/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -48872,7 +48872,7 @@
           <t>F | 246呎 (开放式)
 $426万
 $17,329/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -48880,7 +48880,7 @@
           <t>G | 300呎 (1房)
 $527万
 $17,580/呎
-(24年-12月-16日)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -48888,7 +48888,7 @@
           <t>H | 493呎 (2房)
 $980万
 $19,874/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -48903,7 +48903,7 @@
           <t>A | 440呎 (2房)
 $809万
 $18,384/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -48927,7 +48927,7 @@
           <t>D | 245呎 (开放式)
 $442万
 $18,057/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -48935,7 +48935,7 @@
           <t>E | 247呎 (开放式)
 $421万
 $17,040/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -48943,7 +48943,7 @@
           <t>F | 246呎 (开放式)
 $423万
 $17,207/呎
-(25年-09月-02日)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -48951,7 +48951,7 @@
           <t>G | 300呎 (1房)
 $524万
 $17,457/呎
-(25年-01月-01日)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -48974,7 +48974,7 @@
           <t>A | 440呎 (2房)
 $808万
 $18,359/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -48998,7 +48998,7 @@
           <t>D | 245呎 (开放式)
 $439万
 $17,931/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -49006,7 +49006,7 @@
           <t>E | 247呎 (开放式)
 $418万
 $16,919/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -49014,7 +49014,7 @@
           <t>F | 246呎 (开放式)
 $420万
 $17,085/呎
-(25年-09月-02日)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -49022,7 +49022,7 @@
           <t>G | 300呎 (1房)
 $520万
 $17,333/呎
-(25年-01月-01日)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -49045,7 +49045,7 @@
           <t>A | 440呎 (2房)
 $800万
 $18,177/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -49062,7 +49062,7 @@
           <t>D | 251呎 (开放式)
 $491万
 $19,546/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -49070,7 +49070,7 @@
           <t>E | 247呎 (开放式)
 $415万
 $16,798/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -49078,7 +49078,7 @@
           <t>F | 246呎 (开放式)
 $417万
 $16,967/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -49086,7 +49086,7 @@
           <t>G | 300呎 (1房)
 $516万
 $17,213/呎
-(25年-01月-01日)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="I24" s="24" t="inlineStr">
@@ -49109,7 +49109,7 @@
           <t>A | 440呎 (2房)
 $785万
 $17,845/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -49126,7 +49126,7 @@
           <t>D | 251呎 (开放式)
 $438万
 $17,438/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -49134,7 +49134,7 @@
           <t>E | 247呎 (开放式)
 $412万
 $16,684/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -49142,7 +49142,7 @@
           <t>F | 246呎 (开放式)
 $414万
 $16,850/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -49150,7 +49150,7 @@
           <t>G | 300呎 (1房)
 $513万
 $17,093/呎
-(25年-01月-01日)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -49158,7 +49158,7 @@
           <t>H | 493呎 (2房)
 $955万
 $19,363/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -49173,7 +49173,7 @@
           <t>A | 440呎 (2房)
 $774万
 $17,584/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -49190,7 +49190,7 @@
           <t>D | 251呎 (开放式)
 $435万
 $17,315/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -49198,7 +49198,7 @@
           <t>E | 247呎 (开放式)
 $412万
 $16,660/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -49206,7 +49206,7 @@
           <t>F | 246呎 (开放式)
 $414万
 $16,821/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -49214,7 +49214,7 @@
           <t>G | 300呎 (1房)
 $509万
 $16,973/呎
-(25年-01月-01日)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -49237,7 +49237,7 @@
           <t>A | 440呎 (2房)
 $761万
 $17,295/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -49254,7 +49254,7 @@
           <t>D | 251呎 (开放式)
 $432万
 $17,195/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -49262,7 +49262,7 @@
           <t>E | 247呎 (开放式)
 $409万
 $16,547/呎
-(25年-07月-06日)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -49270,7 +49270,7 @@
           <t>F | 246呎 (开放式)
 $411万
 $16,703/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -49278,7 +49278,7 @@
           <t>G | 300呎 (1房)
 $506万
 $16,853/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -49301,7 +49301,7 @@
           <t>A | 440呎 (2房)
 $747万
 $16,975/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -49318,7 +49318,7 @@
           <t>D | 251呎 (开放式)
 $477万
 $19,008/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -49326,7 +49326,7 @@
           <t>E | 247呎 (开放式)
 $408万
 $16,514/呎
-(25年-07月-10日)</t>
+(25年-07月-11日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -49334,7 +49334,7 @@
           <t>F | 246呎 (开放式)
 $410万
 $16,683/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -49342,7 +49342,7 @@
           <t>G | 300呎 (1房)
 $502万
 $16,737/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="I28" s="24" t="inlineStr">
@@ -49530,7 +49530,7 @@
           <t>D | 305呎 (1房)
 $654万
 $21,439/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -49593,7 +49593,7 @@
           <t>D | 305呎 (1房)
 $648万
 $21,230/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -49656,7 +49656,7 @@
           <t>D | 305呎 (1房)
 $641万
 $21,016/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -49711,7 +49711,7 @@
           <t>C | 244呎 (开放式)
 $574万
 $23,525/呎
-(26年-06月-19日)</t>
+(26年-06月-20日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -49719,7 +49719,7 @@
           <t>D | 305呎 (1房)
 $621万
 $20,357/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -49758,7 +49758,7 @@
           <t>A | 439呎 (2房)
 $1096万
 $24,970/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -49774,7 +49774,7 @@
           <t>C | 244呎 (开放式)
 $557万
 $22,836/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -49782,7 +49782,7 @@
           <t>D | 305呎 (1房)
 $615万
 $20,154/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -49818,10 +49818,10 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 440呎 (2房)
+          <t>A | 439呎 (2房)
 $1319万
-$29,982/呎
-(26年-06月-30日)</t>
+$30,050/呎
+(26年-07月-27日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -49837,7 +49837,7 @@
           <t>C | 244呎 (开放式)
 $552万
 $22,611/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -49845,7 +49845,7 @@
           <t>D | 305呎 (1房)
 $609万
 $19,954/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -49884,7 +49884,7 @@
           <t>A | 439呎 (2房)
 $1274万
 $29,027/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -49900,7 +49900,7 @@
           <t>C | 244呎 (开放式)
 $543万
 $22,270/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -49908,7 +49908,7 @@
           <t>D | 305呎 (1房)
 $606万
 $19,856/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -49932,7 +49932,7 @@
           <t>G | 494呎 (2房)
 $1301万
 $26,342/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -49947,7 +49947,7 @@
           <t>A | 439呎 (2房)
 $1075万
 $24,478/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -49963,7 +49963,7 @@
           <t>C | 244呎 (开放式)
 $547万
 $22,406/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -49971,7 +49971,7 @@
           <t>D | 305呎 (1房)
 $603万
 $19,757/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -50089,7 +50089,7 @@
           <t>C | 244呎 (开放式)
 $541万
 $22,164/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -50097,7 +50097,7 @@
           <t>D | 305呎 (1房)
 $597万
 $19,564/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -50152,7 +50152,7 @@
           <t>C | 244呎 (开放式)
 $550万
 $22,541/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -50160,7 +50160,7 @@
           <t>D | 305呎 (1房)
 $594万
 $19,466/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -50215,7 +50215,7 @@
           <t>C | 244呎 (开放式)
 $542万
 $22,201/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -50223,7 +50223,7 @@
           <t>D | 305呎 (1房)
 $591万
 $19,367/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -50231,7 +50231,7 @@
           <t>E | 305呎 (1房)
 $604万
 $19,797/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -50278,7 +50278,7 @@
           <t>C | 244呎 (开放式)
 $527万
 $21,615/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -50286,7 +50286,7 @@
           <t>D | 305呎 (1房)
 $588万
 $19,269/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -50294,7 +50294,7 @@
           <t>E | 305呎 (1房)
 $614万
 $20,128/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -50325,7 +50325,7 @@
           <t>A | 439呎 (2房)
 $1043万
 $23,756/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -50349,7 +50349,7 @@
           <t>D | 305呎 (1房)
 $585万
 $19,177/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -50357,7 +50357,7 @@
           <t>E | 305呎 (1房)
 $598万
 $19,600/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -50373,7 +50373,7 @@
           <t>G | 494呎 (2房)
 $1219万
 $24,678/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -50388,7 +50388,7 @@
           <t>A | 440呎 (2房)
 $1038万
 $23,584/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -50412,7 +50412,7 @@
           <t>D | 305呎 (1房)
 $582万
 $19,079/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -50420,7 +50420,7 @@
           <t>E | 305呎 (1房)
 $595万
 $19,502/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -50436,7 +50436,7 @@
           <t>G | 494呎 (2房)
 $1213万
 $24,555/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -50451,7 +50451,7 @@
           <t>A | 439呎 (2房)
 $1032万
 $23,519/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -50475,7 +50475,7 @@
           <t>D | 305呎 (1房)
 $579万
 $18,984/呎
-(25年-07月-31日)</t>
+(25年-08月-01日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -50483,7 +50483,7 @@
           <t>E | 305呎 (1房)
 $645万
 $21,151/呎
-(26年-03月-17日)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -50499,7 +50499,7 @@
           <t>G | 494呎 (2房)
 $1387万
 $28,079/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -50514,7 +50514,7 @@
           <t>A | 439呎 (2房)
 $1027万
 $23,401/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -50530,7 +50530,7 @@
           <t>C | 244呎 (开放式)
 $525万
 $21,504/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -50538,7 +50538,7 @@
           <t>D | 305呎 (1房)
 $582万
 $19,098/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -50546,7 +50546,7 @@
           <t>E | 305呎 (1房)
 $589万
 $19,305/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -50562,7 +50562,7 @@
           <t>G | 494呎 (2房)
 $1380万
 $27,941/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -50577,7 +50577,7 @@
           <t>A | 440呎 (2房)
 $1022万
 $23,232/呎
-(25年-06月-10日)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -50593,7 +50593,7 @@
           <t>C | 244呎 (开放式)
 $522万
 $21,402/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -50601,7 +50601,7 @@
           <t>D | 305呎 (1房)
 $573万
 $18,797/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -50609,7 +50609,7 @@
           <t>E | 305呎 (1房)
 $599万
 $19,626/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -50625,7 +50625,7 @@
           <t>G | 494呎 (2房)
 $1195万
 $24,188/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -50656,7 +50656,7 @@
           <t>C | 244呎 (开放式)
 $516万
 $21,148/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -50664,7 +50664,7 @@
           <t>D | 305呎 (1房)
 $569万
 $18,662/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -50672,7 +50672,7 @@
           <t>E | 305呎 (1房)
 $594万
 $19,492/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -50719,7 +50719,7 @@
           <t>C | 244呎 (开放式)
 $509万
 $20,869/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -50727,7 +50727,7 @@
           <t>D | 305呎 (1房)
 $563万
 $18,459/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -50735,7 +50735,7 @@
           <t>E | 305呎 (1房)
 $577万
 $18,905/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -50782,7 +50782,7 @@
           <t>C | 244呎 (开放式)
 $499万
 $20,467/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -50790,7 +50790,7 @@
           <t>D | 305呎 (1房)
 $554万
 $18,148/呎
-(25年-07月-20日)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -50798,7 +50798,7 @@
           <t>E | 305呎 (1房)
 $582万
 $19,066/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -50829,7 +50829,7 @@
           <t>A | 439呎 (2房)
 $1173万
 $26,715/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -50845,7 +50845,7 @@
           <t>C | 244呎 (开放式)
 $496万
 $20,340/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -50853,7 +50853,7 @@
           <t>D | 305呎 (1房)
 $546万
 $17,911/呎
-(25年-07月-29日)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -50861,7 +50861,7 @@
           <t>E | 305呎 (1房)
 $576万
 $18,869/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -50877,7 +50877,7 @@
           <t>G | 494呎 (2房)
 $1162万
 $23,518/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -50916,7 +50916,7 @@
           <t>D | 305呎 (1房)
 $540万
 $17,715/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -50924,7 +50924,7 @@
           <t>E | 305呎 (1房)
 $559万
 $18,325/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -50979,7 +50979,7 @@
           <t>D | 305呎 (1房)
 $534万
 $17,521/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -50987,7 +50987,7 @@
           <t>E | 305呎 (1房)
 $577万
 $18,931/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -51042,7 +51042,7 @@
           <t>D | 305呎 (1房)
 $524万
 $17,174/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -51050,7 +51050,7 @@
           <t>E | 305呎 (1房)
 $570万
 $18,685/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -51222,7 +51222,7 @@
           <t>A | 593呎 (3房)
 $1658万
 $27,966/呎
-(25年-01月-01日)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -51230,7 +51230,7 @@
           <t>B | 306呎 (1房)
 $662万
 $21,631/呎
-(25年-01月-01日)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -51238,7 +51238,7 @@
           <t>C | 447呎 (2房)
 $1010万
 $22,591/呎
-(25年-01月-01日)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -51246,7 +51246,7 @@
           <t>D | 1770呎 (4+房)
 $7080万
 $40,000/呎
-(25年-01月-06日)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="F5" s="25" t="inlineStr"/>
@@ -51312,7 +51312,7 @@
           <t>G | 657呎 (3房)
 $1854万
 $28,221/呎
-(25年-01月-15日)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
     </row>
@@ -51493,7 +51493,7 @@
           <t>F | 705呎 (3房)
 $2185万
 $30,987/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -51548,7 +51548,7 @@
           <t>E | 496呎 (2房)
 $1480万
 $29,829/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -51556,7 +51556,7 @@
           <t>F | 705呎 (3房)
 $2207万
 $31,308/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -51619,7 +51619,7 @@
           <t>F | 705呎 (3房)
 $1946万
 $27,596/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -51674,7 +51674,7 @@
           <t>E | 496呎 (2房)
 $1366万
 $27,546/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -51682,7 +51682,7 @@
           <t>F | 705呎 (3房)
 $1936万
 $27,460/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -51871,7 +51871,7 @@
           <t>F | 705呎 (3房)
 $2153万
 $30,538/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -51879,7 +51879,7 @@
           <t>G | 658呎 (3房)
 $2060万
 $31,301/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -51997,7 +51997,7 @@
           <t>F | 705呎 (3房)
 $2192万
 $31,085/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -52005,7 +52005,7 @@
           <t>G | 658呎 (3房)
 $1995万
 $30,322/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -52052,7 +52052,7 @@
           <t>E | 496呎 (2房)
 $1326万
 $26,736/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -52060,7 +52060,7 @@
           <t>F | 705呎 (3房)
 $1879万
 $26,648/呎
-(25年-04月-27日)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -52068,7 +52068,7 @@
           <t>G | 658呎 (3房)
 $1933万
 $29,372/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -52107,7 +52107,7 @@
           <t>D | 447呎 (2房)
 $1099万
 $24,586/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
@@ -52123,7 +52123,7 @@
           <t>F | 705呎 (3房)
 $2110万
 $29,933/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -52186,7 +52186,7 @@
           <t>F | 705呎 (3房)
 $1860万
 $26,383/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -52249,7 +52249,7 @@
           <t>F | 705呎 (3房)
 $1892万
 $26,834/呎
-(25年-06月-11日)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -52257,7 +52257,7 @@
           <t>G | 658呎 (3房)
 $1904万
 $28,935/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -52312,7 +52312,7 @@
           <t>F | 705呎 (3房)
 $1841万
 $26,119/呎
-(25年-07月-26日)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -52320,7 +52320,7 @@
           <t>G | 658呎 (3房)
 $1678万
 $25,503/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -52548,7 +52548,7 @@
           <t>D | 447呎 (2房)
 $1053万
 $23,548/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
@@ -52564,7 +52564,7 @@
           <t>F | 705呎 (3房)
 $2122万
 $30,104/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -52611,7 +52611,7 @@
           <t>D | 447呎 (2房)
 $1042万
 $23,300/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">

--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -24337,23 +24337,23 @@
       </c>
       <c r="F376" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
-        <v>6440000</v>
+        <v>5796000</v>
       </c>
       <c r="I376" s="5" t="n">
-        <v>26393</v>
+        <v>23754</v>
       </c>
       <c r="J376" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K376" s="5" t="n">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="M376" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N376" s="3" t="inlineStr">
@@ -49429,7 +49429,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -49439,7 +49439,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -49643,12 +49643,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (开放式)
-$644万
-$26,393/呎
-(在售)</t>
+$580万
+$23,754/呎
+(26年-08月-01日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">

--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -33425,7 +33425,7 @@
       </c>
       <c r="F516" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G516" s="3" t="inlineStr">
@@ -33434,10 +33434,10 @@
         </is>
       </c>
       <c r="H516" s="5" t="n">
-        <v>4860000</v>
+        <v>6014000</v>
       </c>
       <c r="I516" s="5" t="n">
-        <v>19918</v>
+        <v>24648</v>
       </c>
       <c r="J516" s="3" t="inlineStr">
         <is>
@@ -33445,10 +33445,10 @@
         </is>
       </c>
       <c r="K516" s="5" t="n">
-        <v>4374000</v>
+        <v>5412600</v>
       </c>
       <c r="L516" s="5" t="n">
-        <v>17926</v>
+        <v>22183</v>
       </c>
       <c r="M516" s="3" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
       </c>
       <c r="F523" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G523" s="3" t="inlineStr">
@@ -33884,10 +33884,10 @@
         </is>
       </c>
       <c r="H523" s="5" t="n">
-        <v>4797000</v>
+        <v>5937000</v>
       </c>
       <c r="I523" s="5" t="n">
-        <v>19660</v>
+        <v>24332</v>
       </c>
       <c r="J523" s="3" t="inlineStr">
         <is>
@@ -33895,10 +33895,10 @@
         </is>
       </c>
       <c r="K523" s="5" t="n">
-        <v>4317300</v>
+        <v>5343300</v>
       </c>
       <c r="L523" s="5" t="n">
-        <v>17694</v>
+        <v>21899</v>
       </c>
       <c r="M523" s="3" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="F530" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G530" s="3" t="inlineStr">
@@ -34334,10 +34334,10 @@
         </is>
       </c>
       <c r="H530" s="5" t="n">
-        <v>4697000</v>
+        <v>5916000</v>
       </c>
       <c r="I530" s="5" t="n">
-        <v>19250</v>
+        <v>24246</v>
       </c>
       <c r="J530" s="3" t="inlineStr">
         <is>
@@ -34345,10 +34345,10 @@
         </is>
       </c>
       <c r="K530" s="5" t="n">
-        <v>4227300</v>
+        <v>5324400</v>
       </c>
       <c r="L530" s="5" t="n">
-        <v>17325</v>
+        <v>21821</v>
       </c>
       <c r="M530" s="3" t="inlineStr">
         <is>
@@ -44055,38 +44055,30 @@
       </c>
       <c r="F677" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G677" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H677" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I677" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H677" s="5" t="n">
+        <v>19892000</v>
+      </c>
+      <c r="I677" s="5" t="n">
+        <v>30277</v>
       </c>
       <c r="J677" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K677" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L677" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K677" s="5" t="n">
+        <v>19892000</v>
+      </c>
+      <c r="L677" s="5" t="n">
+        <v>30277</v>
       </c>
       <c r="M677" s="3" t="inlineStr">
         <is>
@@ -44095,7 +44087,7 @@
       </c>
       <c r="N677" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -49429,12 +49421,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -50903,12 +50895,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>C | 244呎 (开放式)
-$486万
-$19,918/呎
-(已定价未售)</t>
+$601万
+$24,648/呎
+(在售)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -50966,12 +50958,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>C | 244呎 (开放式)
-$480万
-$19,660/呎
-(已定价未售)</t>
+$594万
+$24,332/呎
+(在售)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -51029,12 +51021,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>C | 244呎 (开放式)
-$470万
-$19,250/呎
-(已定价未售)</t>
+$592万
+$24,246/呎
+(在售)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -51145,7 +51137,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -51155,7 +51147,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -52567,12 +52559,12 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="H26" s="24" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 657呎 (3房)
-招标单位
--
-(在售)</t>
+$1989万
+$30,277/呎
+(26年-08月-04日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -24342,7 +24342,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -49640,7 +49640,7 @@
           <t>C | 244呎 (开放式)
 $580万
 $23,754/呎
-(26年-08月-01日)</t>
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">

--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -26379,38 +26379,30 @@
       </c>
       <c r="F407" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H407" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I407" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H407" s="5" t="n">
+        <v>14872000</v>
+      </c>
+      <c r="I407" s="5" t="n">
+        <v>30105</v>
       </c>
       <c r="J407" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K407" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L407" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K407" s="5" t="n">
+        <v>14872000</v>
+      </c>
+      <c r="L407" s="5" t="n">
+        <v>30105</v>
       </c>
       <c r="M407" s="3" t="inlineStr">
         <is>
@@ -26419,7 +26411,7 @@
       </c>
       <c r="N407" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -49421,7 +49413,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -49431,7 +49423,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -49982,12 +49974,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="24" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 494呎 (2房)
-招标单位
--
-(在售)</t>
+$1487万
+$30,105/呎
+(26年-08月-24日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -44043,7 +44043,7 @@
         </is>
       </c>
       <c r="E677" s="4" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F677" s="3" t="inlineStr">
         <is>
@@ -44052,14 +44052,14 @@
       </c>
       <c r="G677" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H677" s="5" t="n">
         <v>19892000</v>
       </c>
       <c r="I677" s="5" t="n">
-        <v>30277</v>
+        <v>30231</v>
       </c>
       <c r="J677" s="3" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>19892000</v>
       </c>
       <c r="L677" s="5" t="n">
-        <v>30277</v>
+        <v>30231</v>
       </c>
       <c r="M677" s="3" t="inlineStr">
         <is>
@@ -52553,10 +52553,10 @@
       </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
-          <t>G | 657呎 (3房)
+          <t>G | 658呎 (3房)
 $1989万
-$30,277/呎
-(26年-08月-04日)</t>
+$30,231/呎
+(26年-08月-27日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -33417,34 +33417,34 @@
       </c>
       <c r="F516" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
-        <v>6014000</v>
+        <v>5413000</v>
       </c>
       <c r="I516" s="5" t="n">
-        <v>24648</v>
+        <v>22184</v>
       </c>
       <c r="J516" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K516" s="5" t="n">
-        <v>5412600</v>
+        <v>5413000</v>
       </c>
       <c r="L516" s="5" t="n">
-        <v>22183</v>
+        <v>22184</v>
       </c>
       <c r="M516" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N516" s="3" t="inlineStr">
@@ -49413,7 +49413,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -49423,7 +49423,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -50887,12 +50887,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (开放式)
-$601万
-$24,648/呎
-(在售)</t>
+$541万
+$22,184/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">

--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -36561,7 +36561,7 @@
       </c>
       <c r="F564" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G564" s="3" t="inlineStr">
@@ -36569,31 +36569,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H564" s="5" t="n">
-        <v>17706000</v>
-      </c>
-      <c r="I564" s="5" t="n">
-        <v>29858</v>
+      <c r="H564" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I564" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J564" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K564" s="5" t="n">
-        <v>15935400</v>
-      </c>
-      <c r="L564" s="5" t="n">
-        <v>26873</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K564" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L564" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M564" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N564" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -37943,7 +37951,7 @@
       </c>
       <c r="F585" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G585" s="3" t="inlineStr">
@@ -37951,31 +37959,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H585" s="5" t="n">
-        <v>17357000</v>
-      </c>
-      <c r="I585" s="5" t="n">
-        <v>29270</v>
+      <c r="H585" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I585" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J585" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K585" s="5" t="n">
-        <v>15621300</v>
-      </c>
-      <c r="L585" s="5" t="n">
-        <v>26343</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K585" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L585" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M585" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N585" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38471,7 +38487,7 @@
       </c>
       <c r="F593" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G593" s="3" t="inlineStr">
@@ -38479,31 +38495,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H593" s="5" t="n">
-        <v>19406000</v>
-      </c>
-      <c r="I593" s="5" t="n">
-        <v>29537</v>
+      <c r="H593" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I593" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J593" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K593" s="5" t="n">
-        <v>17465400</v>
-      </c>
-      <c r="L593" s="5" t="n">
-        <v>26584</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K593" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L593" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M593" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N593" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38557,7 @@
       </c>
       <c r="F594" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G594" s="3" t="inlineStr">
@@ -38541,31 +38565,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H594" s="5" t="n">
-        <v>21295000</v>
-      </c>
-      <c r="I594" s="5" t="n">
-        <v>30206</v>
+      <c r="H594" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I594" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J594" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K594" s="5" t="n">
-        <v>19165500</v>
-      </c>
-      <c r="L594" s="5" t="n">
-        <v>27185</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K594" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L594" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M594" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N594" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39403,7 +39435,7 @@
       </c>
       <c r="F607" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G607" s="3" t="inlineStr">
@@ -39411,31 +39443,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H607" s="5" t="n">
-        <v>19213000</v>
-      </c>
-      <c r="I607" s="5" t="n">
-        <v>29244</v>
+      <c r="H607" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I607" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J607" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K607" s="5" t="n">
-        <v>17291700</v>
-      </c>
-      <c r="L607" s="5" t="n">
-        <v>26319</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K607" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L607" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M607" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N607" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39465,7 +39505,7 @@
       </c>
       <c r="F608" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G608" s="3" t="inlineStr">
@@ -39473,31 +39513,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H608" s="5" t="n">
-        <v>21084000</v>
-      </c>
-      <c r="I608" s="5" t="n">
-        <v>29906</v>
+      <c r="H608" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I608" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J608" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K608" s="5" t="n">
-        <v>18975600</v>
-      </c>
-      <c r="L608" s="5" t="n">
-        <v>26916</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K608" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L608" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M608" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N608" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -41189,7 +41237,7 @@
       </c>
       <c r="F634" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G634" s="3" t="inlineStr">
@@ -41197,31 +41245,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H634" s="5" t="n">
-        <v>16760000</v>
-      </c>
-      <c r="I634" s="5" t="n">
-        <v>28263</v>
+      <c r="H634" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I634" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J634" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K634" s="5" t="n">
-        <v>15084000</v>
-      </c>
-      <c r="L634" s="5" t="n">
-        <v>25437</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K634" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L634" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M634" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N634" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -42587,7 +42643,7 @@
       </c>
       <c r="F655" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G655" s="3" t="inlineStr">
@@ -42595,31 +42651,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H655" s="5" t="n">
-        <v>16510000</v>
-      </c>
-      <c r="I655" s="5" t="n">
-        <v>27841</v>
+      <c r="H655" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I655" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J655" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K655" s="5" t="n">
-        <v>14859000</v>
-      </c>
-      <c r="L655" s="5" t="n">
-        <v>25057</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K655" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L655" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M655" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N655" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -51129,12 +51193,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -51144,7 +51208,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -51432,12 +51496,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>A | 593呎 (3房)
-$1771万
-$29,858/呎
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -51621,12 +51685,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>A | 593呎 (3房)
-$1736万
-$29,270/呎
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -51787,20 +51851,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>F | 705呎 (3房)
-$2130万
-$30,206/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>G | 657呎 (3房)
-$1941万
-$29,537/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -51913,20 +51977,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>F | 705呎 (3房)
-$2108万
-$29,906/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>G | 657呎 (3房)
-$1921万
-$29,244/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -52062,12 +52126,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>A | 593呎 (3房)
-$1676万
-$28,263/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -52251,12 +52315,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>A | 593呎 (3房)
-$1651万
-$27,841/呎
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">

--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="E238" s="4" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>4412000</v>
       </c>
       <c r="I238" s="5" t="n">
-        <v>17862</v>
+        <v>17935</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>4412000</v>
       </c>
       <c r="L238" s="5" t="n">
-        <v>17862</v>
+        <v>17935</v>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
@@ -28022,14 +28022,14 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
-        <v>5500000</v>
+        <v>5440000</v>
       </c>
       <c r="I432" s="5" t="n">
-        <v>22541</v>
+        <v>22295</v>
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
@@ -28037,10 +28037,10 @@
         </is>
       </c>
       <c r="K432" s="5" t="n">
-        <v>5500000</v>
+        <v>5440000</v>
       </c>
       <c r="L432" s="5" t="n">
-        <v>22541</v>
+        <v>22295</v>
       </c>
       <c r="M432" s="3" t="inlineStr">
         <is>
@@ -48341,9 +48341,9 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>E | 247呎 (开放式)
+          <t>E | 246呎 (开放式)
 $441万
-$17,862/呎
+$17,935/呎
 (25年-07月-14日)</t>
         </is>
       </c>
@@ -50198,9 +50198,9 @@
       <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (开放式)
-$550万
-$22,541/呎
-(26年-05月-11日)</t>
+$544万
+$22,295/呎
+(26年-04月-18日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
